--- a/data/trans_orig/P37A$medicoenfermedad-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicoenfermedad-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486150</t>
+          <t>486200</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493209</t>
+          <t>493206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>458499</t>
+          <t>458801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>949768</t>
+          <t>949122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>959032</t>
+          <t>959022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>721654</t>
+          <t>721279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>732420</t>
+          <t>732453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>614413</t>
+          <t>614544</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>623672</t>
+          <t>623889</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1340606</t>
+          <t>1339498</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1354631</t>
+          <t>1354137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15292</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28270</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623376</t>
+          <t>623514</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635752</t>
+          <t>636489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>671116</t>
+          <t>670632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>683842</t>
+          <t>683939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300142</t>
+          <t>1300086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317359</t>
+          <t>1318220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20570</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>33114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>500510</t>
+          <t>499702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>513957</t>
+          <t>513682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>495072</t>
+          <t>495473</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>509441</t>
+          <t>509416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1000788</t>
+          <t>1001675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1019573</t>
+          <t>1019621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38056</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13858</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33753</t>
+          <t>32923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36697</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62919</t>
+          <t>62481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>348654</t>
+          <t>347754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368576</t>
+          <t>368814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370233</t>
+          <t>371063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390128</t>
+          <t>389388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>727777</t>
+          <t>728215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>753999</t>
+          <t>753571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>21461</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37606</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44984</t>
+          <t>44710</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72832</t>
+          <t>72971</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251412</t>
+          <t>250645</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271003</t>
+          <t>271122</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>305328</t>
+          <t>304188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>324099</t>
+          <t>323755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>562685</t>
+          <t>562546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>590533</t>
+          <t>590807</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18274</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>37502</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29008</t>
+          <t>29749</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53096</t>
+          <t>53988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>171402</t>
+          <t>172381</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>191609</t>
+          <t>191861</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310664</t>
+          <t>310547</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326251</t>
+          <t>325919</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>490695</t>
+          <t>489803</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>514783</t>
+          <t>514042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92818</t>
+          <t>93850</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134187</t>
+          <t>134078</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76264</t>
+          <t>75676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114793</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>180170</t>
+          <t>179404</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>236111</t>
+          <t>232890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3142356</t>
+          <t>3142465</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3183725</t>
+          <t>3182693</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3264404</t>
+          <t>3267006</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3302933</t>
+          <t>3303521</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6419630</t>
+          <t>6422851</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6475571</t>
+          <t>6476337</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446535</t>
+          <t>446475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453209</t>
+          <t>453215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420221</t>
+          <t>420242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429216</t>
+          <t>429221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870737</t>
+          <t>870546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>881489</t>
+          <t>881406</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25620</t>
+          <t>26304</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>664913</t>
+          <t>665506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>680415</t>
+          <t>681017</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600751</t>
+          <t>600446</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609266</t>
+          <t>609278</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1271722</t>
+          <t>1271038</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1288426</t>
+          <t>1287591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>17597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>27181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38294</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664677</t>
+          <t>664266</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>677873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>685302</t>
+          <t>683669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>701107</t>
+          <t>701096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1354418</t>
+          <t>1353883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1375695</t>
+          <t>1375863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10620</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29269</t>
+          <t>29180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,49 +4756,49 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>17959</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10381</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29316</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>4,76%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17959</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10634</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29496</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>31</t>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>25376</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51729</t>
+          <t>50586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>585348</t>
+          <t>585437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>603997</t>
+          <t>604098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,47 +4869,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>598240</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>586883</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>605818</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>95,24%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>598240</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>586703</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>605565</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1179087</t>
+          <t>1180230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1205601</t>
+          <t>1205440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20775</t>
+          <t>20673</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42031</t>
+          <t>41525</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45491</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49679</t>
+          <t>48607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78835</t>
+          <t>78394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>387904</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>408654</t>
+          <t>408756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>402309</t>
+          <t>403766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424866</t>
+          <t>425019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>798394</t>
+          <t>798835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>827550</t>
+          <t>828622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38028</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56665</t>
+          <t>56277</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51476</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83155</t>
+          <t>83785</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271758</t>
+          <t>271558</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293474</t>
+          <t>293703</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>297331</t>
+          <t>297719</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>322130</t>
+          <t>324277</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>580627</t>
+          <t>579997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>612306</t>
+          <t>610602</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18109</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40201</t>
+          <t>39176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37433</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39364</t>
+          <t>40464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69543</t>
+          <t>69384</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>209650</t>
+          <t>210675</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>231742</t>
+          <t>232288</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>351546</t>
+          <t>352772</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>372201</t>
+          <t>373343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>569287</t>
+          <t>569446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>599466</t>
+          <t>598366</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104290</t>
+          <t>104014</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149818</t>
+          <t>153414</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,77 +6133,77 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>141406</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>116341</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>164928</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>266564</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>234629</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>305274</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>4,37%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>141406</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>119979</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>166399</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>266564</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>236250</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>304336</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3276961</t>
+          <t>3273365</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3322489</t>
+          <t>3322765</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,82 +6241,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3416903</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3393381</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3441968</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>95,36%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6262</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6718524</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6679814</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6750459</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>95,63%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>96,96%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3416903</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3391910</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3438330</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>96,03%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6262</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6718524</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6680752</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6748838</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9646</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408281</t>
+          <t>408001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418562</t>
+          <t>418565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>386109</t>
+          <t>386685</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394810</t>
+          <t>394750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>797606</t>
+          <t>798789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811775</t>
+          <t>812091</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>578210</t>
+          <t>578092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588564</t>
+          <t>588515</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>551208</t>
+          <t>552417</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561492</t>
+          <t>561606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1135132</t>
+          <t>1135538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1148631</t>
+          <t>1148290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18349</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25132</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657971</t>
+          <t>657575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667091</t>
+          <t>667135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643037</t>
+          <t>642313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655527</t>
+          <t>655703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305351</t>
+          <t>1306065</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1320807</t>
+          <t>1321297</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30463</t>
+          <t>28963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27983</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>25365</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50198</t>
+          <t>49030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>615585</t>
+          <t>617085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>634810</t>
+          <t>635006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>621094</t>
+          <t>622462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>639088</t>
+          <t>638679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1244927</t>
+          <t>1246095</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1269448</t>
+          <t>1269760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26243</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50796</t>
+          <t>51943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34120</t>
+          <t>32960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45377</t>
+          <t>45494</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79117</t>
+          <t>76180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427122</t>
+          <t>425975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>451675</t>
+          <t>450856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>462729</t>
+          <t>463889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>483128</t>
+          <t>483177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>895650</t>
+          <t>898587</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>929390</t>
+          <t>929273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19661</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40348</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15975</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34975</t>
+          <t>34904</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39977</t>
+          <t>38946</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67942</t>
+          <t>68143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293982</t>
+          <t>294341</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314669</t>
+          <t>315611</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342787</t>
+          <t>342858</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>361787</t>
+          <t>362720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>644150</t>
+          <t>643949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>672115</t>
+          <t>673146</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27506</t>
+          <t>27054</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29700</t>
+          <t>30794</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56986</t>
+          <t>56099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229492</t>
+          <t>229944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245380</t>
+          <t>245583</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>364793</t>
+          <t>365128</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>385497</t>
+          <t>386349</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>600181</t>
+          <t>601068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>627467</t>
+          <t>626373</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97872</t>
+          <t>97222</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>140840</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86925</t>
+          <t>86840</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>129041</t>
+          <t>130473</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>197047</t>
+          <t>198917</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>254881</t>
+          <t>256454</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3253510</t>
+          <t>3254072</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3296478</t>
+          <t>3297128</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3415501</t>
+          <t>3414069</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3457617</t>
+          <t>3457702</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6684011</t>
+          <t>6682438</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6741845</t>
+          <t>6739975</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,22 +9700,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t>29620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>395910</t>
+          <t>404047</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377589</t>
+          <t>389615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>307803</t>
+          <t>356631</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295693</t>
+          <t>342493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312270</t>
+          <t>361433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>703713</t>
+          <t>760677</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>686674</t>
+          <t>740685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710712</t>
+          <t>768010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>14050</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>420009</t>
+          <t>473206</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414908</t>
+          <t>466671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422439</t>
+          <t>475747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>503119</t>
+          <t>491366</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495648</t>
+          <t>483324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508383</t>
+          <t>496529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>923128</t>
+          <t>964573</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>913981</t>
+          <t>955326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>929469</t>
+          <t>971678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>27302</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>18203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34938</t>
+          <t>37417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>526189</t>
+          <t>610581</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516959</t>
+          <t>601686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531444</t>
+          <t>615640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>577299</t>
+          <t>606147</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>569929</t>
+          <t>598135</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582760</t>
+          <t>611856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1103488</t>
+          <t>1216727</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1093402</t>
+          <t>1206612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1111469</t>
+          <t>1225826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32581</t>
+          <t>35124</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>25307</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51462</t>
+          <t>47839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32974</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>28777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43327</t>
+          <t>46969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>65555</t>
+          <t>71796</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>57509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85921</t>
+          <t>86542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>855205</t>
+          <t>665493</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836324</t>
+          <t>652778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>873848</t>
+          <t>675310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>679907</t>
+          <t>700214</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669554</t>
+          <t>689917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>688879</t>
+          <t>708109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1535112</t>
+          <t>1365708</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1514746</t>
+          <t>1350962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1562082</t>
+          <t>1379995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>58873</t>
+          <t>65684</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46367</t>
+          <t>52842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71815</t>
+          <t>80619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>48803</t>
+          <t>55123</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40359</t>
+          <t>46434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59472</t>
+          <t>67318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>107676</t>
+          <t>120808</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91480</t>
+          <t>105496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123417</t>
+          <t>141292</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>502361</t>
+          <t>543662</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>489419</t>
+          <t>528727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>514867</t>
+          <t>556504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>499102</t>
+          <t>553732</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>488433</t>
+          <t>541537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>507546</t>
+          <t>562421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1001463</t>
+          <t>1097394</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985722</t>
+          <t>1076910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1017659</t>
+          <t>1112706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36941</t>
+          <t>40557</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28202</t>
+          <t>30993</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47218</t>
+          <t>51258</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47900</t>
+          <t>53390</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22150</t>
+          <t>43799</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78715</t>
+          <t>64587</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>84841</t>
+          <t>93947</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45183</t>
+          <t>80765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114681</t>
+          <t>108489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>331224</t>
+          <t>366523</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320947</t>
+          <t>355822</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>339963</t>
+          <t>376087</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>560468</t>
+          <t>385776</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>529653</t>
+          <t>374579</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>586218</t>
+          <t>395367</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>891692</t>
+          <t>752299</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>861852</t>
+          <t>737757</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>931350</t>
+          <t>765481</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>34836</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27259</t>
+          <t>29220</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>49383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52029</t>
+          <t>57810</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43153</t>
+          <t>47924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62356</t>
+          <t>68826</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>86865</t>
+          <t>95862</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73776</t>
+          <t>83288</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100370</t>
+          <t>112152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>247923</t>
+          <t>272146</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237828</t>
+          <t>260815</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255500</t>
+          <t>280978</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>373802</t>
+          <t>406799</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>363475</t>
+          <t>395783</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382678</t>
+          <t>416685</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>621725</t>
+          <t>678945</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>608220</t>
+          <t>662655</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>634814</t>
+          <t>691519</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>180994</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144690</t>
+          <t>174010</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>213009</t>
+          <t>226084</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>210781</t>
+          <t>236290</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>172014</t>
+          <t>213731</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>238691</t>
+          <t>260319</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>391775</t>
+          <t>433392</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>340406</t>
+          <t>402625</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>436642</t>
+          <t>471890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3278823</t>
+          <t>3335660</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3246808</t>
+          <t>3306678</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3315127</t>
+          <t>3358752</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3501499</t>
+          <t>3500664</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3473589</t>
+          <t>3476635</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3540266</t>
+          <t>3523223</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6780322</t>
+          <t>6836324</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6735455</t>
+          <t>6797826</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6831691</t>
+          <t>6867091</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
